--- a/Benchmark/UrlManual_removed.xlsx
+++ b/Benchmark/UrlManual_removed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -570,12 +570,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.github.com/masih4/NuInsSeg</t>
+          <t>https://github.com/masih4/NuInsSeg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.github.com/masih4/NuInsSeg</t>
+          <t>https://github.com/masih4/NuInsSeg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/ipateam/nuinsseg?datasetId=1911713</t>
+          <t>https://www.kaggle.com/datasets/ipateam/nuinsseg/code?datasetId=1911713</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.github.com/masih4/NuInsSeg</t>
+          <t>https://github.com/masih4/NuInsSeg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.github.com/masih4/NuInsSeg</t>
+          <t>https://github.com/masih4/NuInsSeg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -769,22 +769,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1016/j.media.2020.101786</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.media.2020.101786</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.media.2020.101771</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.media.2020.101771</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.media.2020.101786</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -821,22 +821,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1007/978-3-030-23937-4_2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/978-3-030-23937-4_2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1007/978-3-030-23937-4_9</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1007/978-3-030-23937-4_9</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1007/978-3-030-23937-4_2</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -925,22 +925,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.openml.org/search?type=data&amp;status=active&amp;id=45021</t>
+          <t>https://www.openml.org/search?id=31&amp;sort=runs&amp;status=active&amp;type=data</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>https://www.openml.org/search?id=31&amp;sort=runs&amp;status=active&amp;type=data</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>https://www.openml.org/search?id=45021&amp;status=active&amp;type=data</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>https://www.openml.org/search?id=31&amp;sort=runs&amp;status=active&amp;type=data</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.huggingface.co/datasets/Zihan1004/FNSPID</t>
+          <t>https://huggingface.co/datasets/Zihan1004/FNSPID</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.huggingface.co/datasets/Zihan1004/FNSPID</t>
+          <t>https://huggingface.co/datasets/Zihan1004/FNSPID</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.physionet.org/content/mimiciv/3.1</t>
+          <t>https://physionet.org/content/mimiciv/3.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.physionet.org/content/mimiciv/3.1</t>
+          <t>https://physionet.org/content/mimiciv/3.1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.nips.cc/public/guides/CodeSubmissionPolicy</t>
+          <t>https://nips.cc/public/guides/CodeSubmissionPolicy</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.nips.cc/public/guides/CodeSubmissionPolicy</t>
+          <t>https://nips.cc/public/guides/CodeSubmissionPolicy</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1129,22 +1129,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>https://zenodo.org/doi/10.5281/zenodo.14513612</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/doi/10.5281/zenodo.14513612</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>https://zenodo.org/doi/10.5281/zenodo.4530182</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.zenodo.org/doi/10.5281/zenodo.4530182</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>https://www.zenodo.org/doi/10.5281/zenodo.14513612</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.universe.roboflow.com/face-detection-and-recognition-dataset/droneface</t>
+          <t>https://universe.roboflow.com/face-detection-and-recognition-dataset/droneface</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.universe.roboflow.com/face-detection-and-recognition-dataset/droneface</t>
+          <t>https://universe.roboflow.com/face-detection-and-recognition-dataset/droneface</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1145/3083187.3083214</t>
+          <t>https://doi.org/10.1145/3083187.3083214</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1145/3083187.3083214</t>
+          <t>https://doi.org/10.1145/3083187.3083214</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/fg.2019.8756593</t>
+          <t>https://doi.org/10.1109/fg.2019.8756593</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/FG.2019.8756593</t>
+          <t>https://doi.org/10.1109/FG.2019.8756593</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1953,22 +1953,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>https://doi.org/10.7914/SN/OE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7914/SN/OE</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>https://doi.org/10.7914/SN/OX</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.7914/SN/OX</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.7914/SN/OE</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -2005,22 +2005,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>https://doi.org/10.7914/SN/SL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7914/SN/SL</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>https://doi.org/10.7914/SN/ST</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.7914/SN/ST</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.7914/SN/SL</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023-supplement</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023-supplement</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/ALPARRAY/XT_2014</t>
+          <t>https://doi.org/10.12686/ALPARRAY/XT_2014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/alparray/xt_2014</t>
+          <t>https://doi.org/10.12686/alparray/xt_2014</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/alparray/z3_2015</t>
+          <t>https://doi.org/10.12686/alparray/z3_2015</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/ALPARRAY/Z3_2015</t>
+          <t>https://doi.org/10.12686/ALPARRAY/Z3_2015</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/BW</t>
+          <t>https://doi.org/10.7914/SN/BW</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/BW</t>
+          <t>https://doi.org/10.7914/SN/BW</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.25928/MBX6-HR74</t>
+          <t>https://doi.org/10.25928/MBX6-HR74</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.25928/mbx6-hr74</t>
+          <t>https://doi.org/10.25928/mbx6-hr74</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2634,17 +2634,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/ST</t>
+          <t>https://doi.org/10.7914/SN/ST</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/SL</t>
+          <t>https://doi.org/10.7914/SN/ST</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1994.tb03942.x</t>
+          <t>https://doi.org/10.1111/j.1365-246X.1994.tb03942.x</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1994.tb03942.x</t>
+          <t>https://doi.org/10.1111/j.1365-246X.1994.tb03942.x</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.orfeus-eu.org/data/eida</t>
+          <t>http://www.orfeus-eu.org/data/eida</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.orfeus-eu.org/data/eida</t>
+          <t>http://www.orfeus-eu.org/data/eida</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2837,22 +2837,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1111/j.1365-246X.2008.03985.x</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.1365-246X.2008.03985.x</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1111/j.1365-246X.2008.03919.x</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2008.03919.x</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2008.03985.x</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1016/j.tecto.2013.08.004</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.tecto.2013.08.004</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.tecto.2015.02.004</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.tecto.2015.02.004</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.tecto.2013.08.004</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/ZJ_2019</t>
+          <t>https://doi.org/10.7914/SN/ZJ_2019</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/ZJ_2019</t>
+          <t>https://doi.org/10.7914/SN/ZJ_2019</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.13127/SD/X0FXNH7QFY</t>
+          <t>https://doi.org/10.13127/SD/X0FXNH7QFY</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.13127/SD/X0FXNH7QFY</t>
+          <t>https://doi.org/10.13127/SD/X0FXNH7QFY</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3102,17 +3102,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/OX</t>
+          <t>https://doi.org/10.7914/SN/OX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/OE</t>
+          <t>https://doi.org/10.7914/SN/OX</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.13127/SD/FBBBTDTD6Q</t>
+          <t>https://doi.org/10.13127/SD/FBBBTDTD6Q</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.13127/SD/fBBBtDtd6q</t>
+          <t>https://doi.org/10.13127/SD/fBBBtDtd6q</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1991.tb06724.x</t>
+          <t>https://doi.org/10.1111/j.1365-246X.1991.tb06724.x</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1991.tb06724.x</t>
+          <t>https://doi.org/10.1111/j.1365-246X.1991.tb06724.x</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7937575</t>
+          <t>https://doi.org/10.5281/zenodo.7937575</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7937575</t>
+          <t>https://doi.org/10.5281/zenodo.7937575</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3357,22 +3357,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1111/j.1365-246X.2007.03706.x</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.1365-246X.2007.03706.x</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1111/j.1365-246X.2007.03373.x</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2007.03373.x</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2007.03706.x</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7695125</t>
+          <t>https://doi.org/10.5281/zenodo.7695125</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7695125</t>
+          <t>https://doi.org/10.5281/zenodo.7695125</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/NI</t>
+          <t>https://doi.org/10.7914/SN/NI</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/NI</t>
+          <t>https://doi.org/10.7914/SN/NI</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.15778/RESIF.FR</t>
+          <t>https://doi.org/10.15778/RESIF.FR</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.15778/RESIF.FR</t>
+          <t>https://doi.org/10.15778/RESIF.FR</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3540,22 +3540,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/j.1365-246X.2006.03086.x</t>
+          <t>https://doi.org/10.7914/SN/SL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>Repositorio / red de datos</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Referencia bibliográfica</t>
+          <t>Datos sísmicos / red</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3565,22 +3565,22 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/j.1365-246X.2006.03086.x</t>
+          <t>https://doi.org/10.7914/SN/SL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2006.03086.x</t>
+          <t>https://doi.org/10.7914/SN/SL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2008.03985.x</t>
+          <t>https://doi.org/10.7914/SN/SL</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7914/SN/SL</t>
+          <t>https://doi.org/10.12686/SED/NETWORKS/CH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3617,17 +3617,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7914/SN/SL</t>
+          <t>https://doi.org/10.12686/SED/NETWORKS/CH</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/SL</t>
+          <t>https://doi.org/10.12686/SED/NETWORKS/CH</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/SL</t>
+          <t>https://doi.org/10.12686/SED/NETWORKS/CH</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3644,22 +3644,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://doi.org/10.12686/SED/NETWORKS/CH</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Repositorio / red de datos</t>
+          <t>DOI URL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Datos sísmicos / red</t>
+          <t>Artículo / suplemento</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3669,17 +3669,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://doi.org/10.12686/SED/NETWORKS/CH</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/SED/NETWORKS/CH</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/SED/NETWORKS/CH</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3696,22 +3696,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.7914/SN/OE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>Repositorio / red de datos</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Artículo / suplemento</t>
+          <t>Datos sísmicos / red</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3721,17 +3721,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.7914/SN/OE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.7914/SN/OE</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.7914/SN/OE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7914/SN/OE</t>
+          <t>https://doi.org/10.15778/RESIF.YP2012</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3773,17 +3773,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7914/SN/OE</t>
+          <t>https://doi.org/10.15778/RESIF.YP2012</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/OE</t>
+          <t>https://doi.org/10.15778/RESIF.YP2012</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/OE</t>
+          <t>https://doi.org/10.15778/RESIF.YP2012</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3800,22 +3800,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://doi.org/10.15778/RESIF.YP2012</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Repositorio / red de datos</t>
+          <t>DOI URL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Datos sísmicos / red</t>
+          <t>Artículo / suplemento</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3825,17 +3825,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://doi.org/10.15778/RESIF.YP2012</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.15778/RESIF.YP2012</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.15778/RESIF.YP2012</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3847,17 +3847,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>essd-15-2117-2023.pdf</t>
+          <t>essd-16-525-2024.pdf</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>Artículo / DOI</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3865,29 +3865,25 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Artículo / suplemento</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>essd-15-2117-2023.pdf</t>
+          <t>essd-16-525-2024.pdf</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3930,12 +3926,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3978,12 +3974,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4026,12 +4022,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4074,12 +4070,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4122,12 +4118,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4170,12 +4166,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4218,12 +4214,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4266,12 +4262,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4314,12 +4310,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4362,12 +4358,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4410,12 +4406,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4432,20 +4428,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Artículo / DOI</t>
+          <t>Repositorio de datos (DOI)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Dataset principal: presupuestos de nutrientes N/P/K</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -4453,17 +4453,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://www.fao.org/faostat/en/#data/ESB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Repositorio de datos (DOI)</t>
+          <t>Base de datos / documentación FAO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dataset principal: presupuestos de nutrientes N/P/K</t>
+          <t>Agricultura / FAOSTAT / nutrientes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://www.fao.org/faostat/en/#data/ESB</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://www.fao.org/faostat/en</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://www.fao.org/faostat/en</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4532,24 +4532,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data/ESB</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024-supplement</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Base de datos / documentación FAO</t>
+          <t>Suplemento del artículo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Agricultura / FAOSTAT / nutrientes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -4557,22 +4553,22 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data/ESB</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024-supplement</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024-supplement</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar</t>
         </is>
       </c>
     </row>
@@ -4584,20 +4580,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024-supplement</t>
+          <t>https://www.fao.org/faostat/en/#data/ESB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Suplemento del artículo</t>
+          <t>Base de datos / documentación FAO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Agricultura / FAOSTAT / nutrientes</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -4605,22 +4605,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024-supplement</t>
+          <t>https://www.fao.org/faostat/en/#data/ESB</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024-supplement</t>
+          <t>https://www.fao.org/faostat/en</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://www.fao.org/faostat/en</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -4632,24 +4632,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data/ESB</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Base de datos / documentación FAO</t>
+          <t>Artículo / DOI</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Agricultura / FAOSTAT / nutrientes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -4657,17 +4653,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data/ESB</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4684,20 +4680,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.7133336</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Artículo / DOI</t>
+          <t>Repositorio/código (DOI)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Código o coeficientes del estudio</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -4705,22 +4705,22 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.7133340</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.7133340</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.7133336</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.7133336</t>
+          <t>https://www.fao.org/faostat/en/#data/ESB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Repositorio/código (DOI)</t>
+          <t>Base de datos / documentación FAO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Código o coeficientes del estudio</t>
+          <t>Agricultura / FAOSTAT / nutrientes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4757,22 +4757,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.7133336</t>
+          <t>https://www.fao.org/faostat/en/#data/ESB</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7133336</t>
+          <t>https://www.fao.org/faostat/en</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7133340</t>
+          <t>https://www.fao.org/faostat/en</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data/ESB</t>
+          <t>https://www.fao.org/faostat/en/#data</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data/ESB</t>
+          <t>https://www.fao.org/faostat/en/#data</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4836,24 +4836,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Base de datos / documentación FAO</t>
+          <t>Artículo / DOI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Agricultura / FAOSTAT / nutrientes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -4861,17 +4857,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en/#data</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4888,20 +4884,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.10511851</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Artículo / DOI</t>
+          <t>Repositorio/código (DOI)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Código o coeficientes del estudio</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -4909,17 +4909,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.10511851</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.10511851</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5281/zenodo.10511851</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.10511851</t>
+          <t>https://doi.org/10.5281/zenodo.10491880</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4961,22 +4961,22 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.10511851</t>
+          <t>https://doi.org/10.5281/zenodo.10491879</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.10511851</t>
+          <t>https://doi.org/10.5281/zenodo.10491879</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.10511851</t>
+          <t>https://doi.org/10.5281/zenodo.10491880</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -4988,12 +4988,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.10491880</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Repositorio/código (DOI)</t>
+          <t>Repositorio de datos (DOI)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Código o coeficientes del estudio</t>
+          <t>Dataset principal: presupuestos de nutrientes N/P/K</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5013,22 +5013,22 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.10491880</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.10491880</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.10491879</t>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -5040,24 +5040,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://doi.org/10.5194/essd-9-149-2017</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Repositorio de datos (DOI)</t>
+          <t>Referencia DOI</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Dataset principal: presupuestos de nutrientes N/P/K</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>essd-16-525-2024.pdf</t>
@@ -5065,22 +5061,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://doi.org/10.5194/essd-9-181-2017</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://doi.org/10.5194/essd-9-181-2017</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.hx3ffbgkh</t>
+          <t>https://doi.org/10.5194/essd-9-149-2017</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-9-149-2017</t>
+          <t>https://doi.org/10.1007/s11104-021-05167-6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5113,22 +5109,22 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-9-149-2017</t>
+          <t>https://doi.org/10.1007/s11104-021-05166-7</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-9-149-2017</t>
+          <t>https://doi.org/10.1007/s11104-021-05166-7</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-9-181-2017</t>
+          <t>https://doi.org/10.1007/s11104-021-05167-6</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -5140,12 +5136,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11104-021-05167-6</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Referencia DOI</t>
+          <t>Artículo / DOI</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5161,22 +5157,22 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11104-021-05167-6</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11104-021-05167-6</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11104-021-05166-7</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5210,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5231,12 +5227,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>essd-16-525-2024.pdf</t>
+          <t>essd-18-2397-2026.pdf</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5252,22 +5248,22 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>essd-16-525-2024.pdf</t>
+          <t>essd-18-2397-2026.pdf</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5310,12 +5306,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5358,12 +5354,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5406,12 +5402,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5454,12 +5450,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5502,12 +5498,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5550,12 +5546,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5598,12 +5594,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5646,12 +5642,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5694,12 +5690,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5742,12 +5738,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5790,12 +5786,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5838,12 +5834,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5886,12 +5882,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5934,12 +5930,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5956,20 +5952,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Artículo / DOI</t>
+          <t>Dataset / Zenodo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Contrails / satellite imagery</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>essd-18-2397-2026.pdf</t>
@@ -5977,17 +5977,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17669443</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dataset / Zenodo</t>
+          <t>Portal de datos / EUMETSAT</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Contrails / satellite imagery</t>
+          <t>Satellite data</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6029,17 +6029,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17669443</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17669443</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17669443</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6056,24 +6056,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-18-1115-2025</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portal de datos / EUMETSAT</t>
+          <t>Referencia / DOI</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Satellite data</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>essd-18-2397-2026.pdf</t>
@@ -6081,17 +6077,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-18-1115-2025</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-18-1115-2025</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://www.user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-18-1115-2025</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6108,12 +6104,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/amt-18-1115-2025</t>
+          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Referencia / DOI</t>
+          <t>Documento / guía</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6129,17 +6125,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/amt-18-1115-2025</t>
+          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-18-1115-2025</t>
+          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-18-1115-2025</t>
+          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6156,20 +6152,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Documento / guía</t>
+          <t>Portal de datos / EUMETSAT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Satellite data</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>essd-18-2397-2026.pdf</t>
@@ -6177,17 +6177,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://www.user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6256,24 +6256,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-17-5161-2024</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portal de datos / EUMETSAT</t>
+          <t>Referencia / DOI</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Satellite data</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>essd-18-2397-2026.pdf</t>
@@ -6281,17 +6277,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-17-5161-2024</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-17-5161-2024</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+          <t>https://doi.org/10.5194/amt-17-5161-2024</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6308,7 +6304,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/amt-17-5161-2024</t>
+          <t>https://doi.org/10.1088/1748-9326/ac26f0</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6329,17 +6325,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/amt-17-5161-2024</t>
+          <t>https://doi.org/10.1088/1748-9326/ac26f0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-17-5161-2024</t>
+          <t>https://doi.org/10.1088/1748-9326/ac26f0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-17-5161-2024</t>
+          <t>https://doi.org/10.1088/1748-9326/ac26f0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6356,17 +6352,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1088/1748-9326/ac26f0</t>
+          <t>https://doi.org/10.5281/zenodo.19327966</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Referencia / DOI</t>
+          <t>Software / Zenodo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -6377,17 +6373,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1088/1748-9326/ac26f0</t>
+          <t>https://doi.org/10.5281/zenodo.19327966</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1088/1748-9326/ac26f0</t>
+          <t>https://doi.org/10.5281/zenodo.19327966</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1088/1748-9326/ac26f0</t>
+          <t>https://doi.org/10.5281/zenodo.19327966</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6404,20 +6400,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.19327966</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Software / Zenodo</t>
+          <t>Dataset / Zenodo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Contrails / satellite imagery</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>essd-18-2397-2026.pdf</t>
@@ -6425,17 +6425,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.19327966</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.19327966</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.19327966</t>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6452,24 +6452,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17669443</t>
+          <t>https://doi.org/10.1175/1520-0477(2002)083&lt;0977:AITMSG&gt;2.3.CO;2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dataset / Zenodo</t>
+          <t>Referencia / DOI</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Contrails / satellite imagery</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>essd-18-2397-2026.pdf</t>
@@ -6477,17 +6473,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17669443</t>
+          <t>https://doi.org/10.1175/1520-0477(2002)083&lt;0977:AITMSG&gt;2.3.CO;2</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17669443</t>
+          <t>https://doi.org/10.1175/1520-0477(2002)083</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17669443</t>
+          <t>https://doi.org/10.1175/1520-0477(2002)083</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6504,7 +6500,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1175/1520-0477(2002)083&lt;0977:AITMSG&gt;2.3.CO;2</t>
+          <t>https://doi.org/10.5194/amt-10-4317-2017</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6525,39 +6521,39 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1175/1520-0477(2002)083&lt;0977:AITMSG&gt;2.3.CO;2</t>
+          <t>https://doi.org/10.5194/amt-10-3547-2017</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/1520-0477(2002)083</t>
+          <t>https://doi.org/10.5194/amt-10-3547-2017</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/1520-0477(2002)083</t>
+          <t>https://doi.org/10.5194/amt-10-4317-2017</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>essd-18-2397-2026.pdf</t>
+          <t>s41597-025-04605-9.pdf</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/amt-10-4317-2017</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Referencia / DOI</t>
+          <t>DOI URL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6565,30 +6561,34 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>essd-18-2397-2026.pdf</t>
+          <t>s41597-025-04605-9.pdf</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/amt-10-4317-2017</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-10-4317-2017</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-10-3547-2017</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Artículo</t>
+          <t>Repositorio de datos / Zenodo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6729,17 +6729,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6756,47 +6756,47 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5281/zenodo.13327931</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>DOI URL</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Repositorio de datos / Zenodo</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>s41597-025-04605-9.pdf</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>DOI URL</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Repositorio de datos / Zenodo</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>s41597-025-04605-9.pdf</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
-        </is>
-      </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13327931</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -6808,47 +6808,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5281/zenodo.13327651</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DOI URL</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Repositorio de datos / Zenodo</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>s41597-025-04605-9.pdf</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5281/zenodo.13327931</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>DOI URL</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Repositorio de datos / Zenodo</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>s41597-025-04605-9.pdf</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>https://doi.org/10.5281/zenodo.13327931</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327931</t>
-        </is>
-      </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13327651</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -6860,47 +6860,47 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5281/zenodo.13327958</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DOI URL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Repositorio de datos / Zenodo</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>s41597-025-04605-9.pdf</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5281/zenodo.13327651</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>DOI URL</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Repositorio de datos / Zenodo</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>s41597-025-04605-9.pdf</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>https://doi.org/10.5281/zenodo.13327651</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327651</t>
-        </is>
-      </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327958</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -6912,47 +6912,47 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DOI URL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Repositorio de datos / Zenodo</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>s41597-025-04605-9.pdf</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5281/zenodo.13327958</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>DOI URL</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Repositorio de datos / Zenodo</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>s41597-025-04605-9.pdf</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>https://doi.org/10.5281/zenodo.13327958</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327958</t>
-        </is>
-      </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327682</t>
+          <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6984,27 +6984,27 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>s41597-025-04605-9.pdf</t>
+          <t>essd-18-2397-2026.pdf</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327682</t>
+          <t>https://doi.org/10.5281/zenodo.19327966</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327682</t>
+          <t>https://doi.org/10.5281/zenodo.19327966</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7016,47 +7016,47 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5281/zenodo.13327692</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DOI URL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Repositorio de datos / Zenodo</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>s41597-025-04605-9.pdf</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>DOI URL</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Repositorio de datos / Zenodo</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>s41597-025-04605-9.pdf</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327961</t>
-        </is>
-      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.19327966</t>
+          <t>https://doi.org/10.5281/zenodo.13327692</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327692</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Zenodo</t>
+          <t>Artículo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327692</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327692</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13327988</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Artículo</t>
+          <t>Repositorio de datos / Zenodo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7145,22 +7145,22 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13327692</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13327692</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13327988</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7202,17 +7202,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329670</t>
+          <t>https://doi.org/10.5281/zenodo.13329670</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13329670</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -7224,22 +7224,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327988</t>
+          <t>https://imagej.net/software/fiji/</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>Software / documentación</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Zenodo</t>
+          <t>Software / formato</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7249,22 +7249,22 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327988</t>
+          <t>https://imagej.net/software/fiji/</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327988</t>
+          <t>https://imagej.net/software/fiji</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://imagej.net/software/fiji</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329670</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Zenodo</t>
+          <t>Artículo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7301,22 +7301,22 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329670</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329670</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://imagej.net/software/fiji/</t>
+          <t>https://dawnsci.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7353,17 +7353,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://imagej.net/software/fiji/</t>
+          <t>https://dawnsci.org</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.imagej.net/software/fiji</t>
+          <t>https://dawnsci.org</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://www.imagej.net/software/fiji</t>
+          <t>https://dawnsci.org</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7432,22 +7432,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://dawnsci.org</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Software / documentación</t>
+          <t>DOI URL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Software / formato</t>
+          <t>Repositorio de datos / Zenodo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7457,17 +7457,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://dawnsci.org</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.dawnsci.org</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://www.dawnsci.org</t>
+          <t>https://doi.org/10.5281/zenodo.13329639</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329670</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Artículo</t>
+          <t>Repositorio de datos / Zenodo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329670</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329670</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>https://doi.org/10.5281/zenodo.13329670</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13329625</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7561,22 +7561,22 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13329625</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329670</t>
+          <t>https://doi.org/10.5281/zenodo.14245751</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7613,22 +7613,22 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329670</t>
+          <t>https://doi.org/10.5281/zenodo.14245751</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329670</t>
+          <t>https://doi.org/10.5281/zenodo.14245751</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.14245751</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329625</t>
+          <t>https://doi.org/10.5281/zenodo.13327891</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7665,22 +7665,22 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13329625</t>
+          <t>https://doi.org/10.5281/zenodo.13327891</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329625</t>
+          <t>https://doi.org/10.5281/zenodo.13327891</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13327891</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.14245751</t>
+          <t>https://doi.org/10.5281/zenodo.12206815</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.14245751</t>
+          <t>https://doi.org/10.5281/zenodo.12206815</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14245751</t>
+          <t>https://doi.org/10.5281/zenodo.12206815</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14245751</t>
+          <t>https://doi.org/10.5281/zenodo.12206815</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327931</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7769,22 +7769,22 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327988</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327988</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327931</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.12206815</t>
+          <t>https://doi.org/10.5281/zenodo.13327651</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7821,22 +7821,22 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.12206815</t>
+          <t>https://doi.org/10.5281/zenodo.13327931</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.12206815</t>
+          <t>https://doi.org/10.5281/zenodo.13327931</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.12206815</t>
+          <t>https://doi.org/10.5281/zenodo.13327651</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327931</t>
+          <t>https://doi.org/10.5281/zenodo.13327958</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7873,22 +7873,22 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327931</t>
+          <t>https://doi.org/10.5281/zenodo.13327651</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327931</t>
+          <t>https://doi.org/10.5281/zenodo.13327651</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>https://doi.org/10.5281/zenodo.13327958</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327651</t>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7925,22 +7925,22 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327651</t>
+          <t>https://doi.org/10.5281/zenodo.13327958</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327651</t>
+          <t>https://doi.org/10.5281/zenodo.13327958</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327958</t>
+          <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7977,22 +7977,22 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327958</t>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327958</t>
+          <t>https://doi.org/10.5281/zenodo.13327682</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327682</t>
+          <t>https://doi.org/10.5281/zenodo.13327692</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8029,22 +8029,22 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327682</t>
+          <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327682</t>
+          <t>https://doi.org/10.5281/zenodo.13327961</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
+          <t>https://doi.org/10.5281/zenodo.13327692</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327961</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Zenodo</t>
+          <t>Artículo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327961</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327961</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.19327966</t>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -8108,116 +8108,116 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327692</t>
+          <t>http://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>Licencia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Zenodo</t>
+          <t>Licencia</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>s41597-025-04605-9.pdf</t>
+          <t>Otterloo-Burda-Utrecht_Housing_dataset_CSR2025.pdf</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.13327692</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327692</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>s41597-026-06866-4_reference.pdf</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>http://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Licencia</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Licencia</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
           <t>s41597-025-04605-9.pdf</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>DOI URL</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Artículo</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>s41597-025-04605-9.pdf</t>
-        </is>
-      </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>s41597-025-04605-9.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004F039/</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Licencia</t>
+          <t>Metadata USGS EarthExplorer</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8227,32 +8227,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Licencia</t>
+          <t>Metadatos de imágenes satelitales</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>s41597-025-04605-9.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004A040</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004A040</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004F039</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full/</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Licencia</t>
+          <t>Metadata USGS EarthExplorer</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Licencia</t>
+          <t>Metadatos de imágenes satelitales</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8289,22 +8289,22 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004F039</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004F039</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004F039/</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Metadata USGS EarthExplorer</t>
+          <t>Repositorio Figshare</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Metadatos de imágenes satelitales</t>
+          <t>Repositorio de dataset / código</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8341,22 +8341,22 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004F039/</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004F039</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://www.earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004A040</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://earthexplorer.usgs.gov/scene/metadata/full/</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Metadata USGS EarthExplorer</t>
+          <t>Repositorio Figshare</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Metadatos de imágenes satelitales</t>
+          <t>Repositorio de dataset / código</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8393,22 +8393,22 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://earthexplorer.usgs.gov/scene/metadata/full/</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.earthexplorer.usgs.gov/scene/metadata/full</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://www.earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004A040</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -8420,47 +8420,47 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41467-021-24180-y</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Repositorio Figshare</t>
+          <t>DOI de referencia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Repositorio de dataset / código</t>
+          <t>Referencia bibliográfica</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>s41597-025-04605-9.pdf</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41467-021-26480-9</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41467-021-26480-9</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41467-021-24180-y</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -8472,47 +8472,47 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.5194/essd-15-2841-2023</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Repositorio Figshare</t>
+          <t>DOI de referencia</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Repositorio de dataset / código</t>
+          <t>Referencia bibliográfica</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>essd-15-2117-2023.pdf</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.5194/essd-15-2117-2023</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.5194/essd-15-2841-2023</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -8524,22 +8524,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41467-021-24180-y</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DOI de referencia</t>
+          <t>Repositorio Figshare</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Referencia bibliográfica</t>
+          <t>Repositorio de dataset / código</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8549,22 +8549,22 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41467-021-24180-y</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41467-021-24180-y</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41467-021-26480-9</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -8576,47 +8576,47 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5194/essd-15-3819-2023</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DOI de referencia</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Referencia bibliográfica</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>s41597-026-06866-4_reference.pdf</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5194/essd-15-2841-2023</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>DOI de referencia</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Referencia bibliográfica</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>https://doi.org/10.5194/essd-15-2841-2023</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5194/essd-15-2841-2023</t>
-        </is>
-      </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
+          <t>https://doi.org/10.5194/essd-15-3819-2023</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -8628,22 +8628,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Repositorio Figshare</t>
+          <t>DOI del artículo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Repositorio de dataset / código</t>
+          <t>Artículo</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8653,17 +8653,17 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -8866,12 +8866,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -9767,52 +9767,52 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
+          <t>s41597-026-06867-3.pdf</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>DOI / enlace persistente</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Referencia bibliográfica DOI</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
           <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>DOI del artículo</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Artículo</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>https://doi.org/10.1038/s41597-026-06866-4</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
-        </is>
-      </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -9854,17 +9854,17 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -9906,17 +9906,17 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -9958,17 +9958,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10010,17 +10010,17 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10062,17 +10062,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10114,17 +10114,17 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10166,17 +10166,17 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Referencia bibliográfica DOI</t>
+          <t>Repositorio de datos / Zenodo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -10213,22 +10213,22 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Zenodo</t>
+          <t>Referencia bibliográfica DOI</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10265,22 +10265,22 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Referencia bibliográfica DOI</t>
+          <t>Repositorio de datos / Zenodo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -10317,22 +10317,22 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.7554/eLife.45133</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Zenodo</t>
+          <t>Referencia bibliográfica DOI</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10369,17 +10369,17 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.7554/eLife.45133</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.7554/eLife.45133</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17992421</t>
+          <t>https://doi.org/10.7554/eLife.45133</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7554/eLife.45133</t>
+          <t>https://doi.org/10.6084/M9.FIGSHARE.12033672.V58</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -10406,37 +10406,37 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Referencia bibliográfica DOI</t>
+          <t>Repositorio de datos / Figshare</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>s41597-026-06867-3.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7554/eLife.45133</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7554/eLife.45133</t>
+          <t>https://doi.org/10.6084/m9.figshare.30017944</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7554/eLife.45133</t>
+          <t>https://doi.org/10.6084/M9</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/M9.FIGSHARE.12033672.V58</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -10458,12 +10458,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Repositorio de datos / Figshare</t>
+          <t>Referencia bibliográfica DOI</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10473,22 +10473,22 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/M9.FIGSHARE.12033672.V58</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/M9</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10500,12 +10500,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+          <t>http://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DOI / enlace persistente</t>
+          <t>Licencia</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10515,49 +10515,49 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Referencia bibliográfica DOI</t>
+          <t>Licencia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>s41597-026-06867-3.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06867-3</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>s41597-026-06867-3.pdf</t>
+          <t>s41597-026-07203-5_reference.pdf</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://doi.org/10.1038/s41597-026-07203-5</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Licencia</t>
+          <t>DOI URL</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10567,27 +10567,27 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Licencia</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>s41597-026-06867-3.pdf</t>
+          <t>s41597-026-07203-5_reference.pdf</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://doi.org/10.1038/s41597-026-07203-5</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://doi.org/10.1038/s41597-026-07203-5</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://doi.org/10.1038/s41597-026-07203-5</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -10604,22 +10604,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-07203-5</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>Repositorio/Dataset</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Water distribution / leak detection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -10629,17 +10629,17 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-07203-5</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-07203-5</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-07203-5</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -10686,12 +10686,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -10755,47 +10755,43 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>s41597-026-07203-5_reference.pdf</t>
+          <t>s41597-026-07353-6_reference.pdf</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.1038/s41597-026-07353-6</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Repositorio/Dataset</t>
+          <t>DOI URL</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Water distribution / leak detection</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>s41597-026-07203-5_reference.pdf</t>
+          <t>s41597-026-07353-6_reference.pdf</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.1038/s41597-026-07353-6</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.1038/s41597-026-07353-6</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15096167</t>
+          <t>https://doi.org/10.1038/s41597-026-07353-6</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -10812,12 +10808,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-07353-6</t>
+          <t>http://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>URL web</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10825,30 +10821,34 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Licencia</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>s41597-026-07353-6_reference.pdf</t>
+          <t>s41597-026-06867-3.pdf</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-026-07353-6</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-07353-6</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-07353-6</t>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -10860,22 +10860,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>URL web</t>
+          <t>DOI URL</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Licencia</t>
+          <t>Dataset de aguas subterráneas</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -10885,17 +10885,17 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>http://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.1038/s41597-023-02895-5</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -11078,54 +11078,50 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Dataset de aguas subterráneas</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>s41597-026-07353-6_reference.pdf</t>
+          <t>essd-16-525-2024.pdf</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.1038/s41597-023-02385-8</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.1038/s41597-023-02385-8</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
+          <t>https://doi.org/10.1038/s41597-023-02895-5</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>s41597-026-07353-6_reference.pdf</t>
+          <t>usenixsecurity24-appendix-lopez-morales.pdf</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-023-02895-5</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DOI URL</t>
+          <t>GitHub / dataset</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11133,30 +11129,34 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Systematic literature review dataset</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>s41597-026-07353-6_reference.pdf</t>
+          <t>usenixsecurity24-appendix-lopez-morales.pdf</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-023-02895-5</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-023-02895-5</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-023-02385-8</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -11168,22 +11168,22 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>GitHub / dataset</t>
+          <t>GitHub / taxonomy artifact</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Systematic literature review dataset</t>
+          <t>Threat taxonomy / ICS2 Matrix</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11193,17 +11193,17 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/plc-sok-dataset</t>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/plc-sok-dataset</t>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -11220,22 +11220,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/ics2matrix</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>GitHub / taxonomy artifact</t>
+          <t>GitHub / dataset</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Threat taxonomy / ICS2 Matrix</t>
+          <t>Systematic literature review dataset</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11245,22 +11245,22 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/ics2matrix</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/plc-sok-dataset</t>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -11324,22 +11324,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
+          <t>https://github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>GitHub / dataset</t>
+          <t>GitHub / taxonomy artifact</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Systematic literature review dataset</t>
+          <t>Threat taxonomy / ICS2 Matrix</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -11349,17 +11349,17 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
+          <t>https://github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/plc-sok-dataset/tree/ebeb195e5969d99061302950bb173c6d997be30e</t>
+          <t>https://github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/plc-sok-dataset</t>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11406,12 +11406,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
+          <t>https://github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix</t>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
+          <t>https://github.com/efrenlopezm/ics2matrix?tab=readme-ov-file#how-do-i-use-the-ics2-matrix</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -11453,17 +11453,17 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
+          <t>https://github.com/efrenlopezm/ics2matrix?tab=readme-ov-file#how-do-i-use-the-ics2-matrix</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix/tree/e60ba236a45483bec81b16677b8c71314267f235</t>
+          <t>https://github.com/efrenlopezm/ics2matrix?tab=readme-ov-file</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix</t>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -11475,47 +11475,43 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>usenixsecurity24-appendix-lopez-morales.pdf</t>
+          <t>essd-13-5337-2021.pdf</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/ics2matrix?tab=readme-ov-file#how-do-i-use-the-ics2-matrix</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>GitHub / taxonomy artifact</t>
+          <t>URL DOI</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Threat taxonomy / ICS2 Matrix</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>usenixsecurity24-appendix-lopez-morales.pdf</t>
+          <t>essd-13-5337-2021.pdf</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://github.com/efrenlopezm/ics2matrix?tab=readme-ov-file#how-do-i-use-the-ics2-matrix</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -11540,7 +11536,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
@@ -11554,12 +11554,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -11584,7 +11584,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
@@ -11598,12 +11602,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -11628,7 +11632,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
@@ -11642,12 +11650,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -11664,7 +11672,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -11672,8 +11680,16 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Repositorio de datos</t>
+        </is>
+      </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>essd-13-5337-2021.pdf</t>
@@ -11681,17 +11697,17 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -11708,7 +11724,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -11718,14 +11734,10 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Repositorio de datos</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>essd-13-5337-2021.pdf</t>
@@ -11733,17 +11745,17 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.6hdr7sqzx</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.6hdr7sqzx</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -11768,7 +11780,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
@@ -11782,12 +11798,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -11812,7 +11828,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
@@ -11826,12 +11846,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -11856,7 +11876,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
@@ -11870,12 +11894,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -11900,7 +11924,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
@@ -11914,12 +11942,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -11944,7 +11972,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
@@ -11958,12 +11990,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -11980,7 +12012,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021-supplement</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -11988,7 +12020,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
@@ -11997,22 +12033,22 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5194/essd-13-5337-2021-supplement</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5194/essd-13-5337-2021-supplement</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
-        </is>
-      </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12060,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-13-5337-2021-supplement</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -12032,7 +12068,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
@@ -12041,22 +12081,22 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-13-5337-2021-supplement</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021-supplement</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_exact</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12116,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
@@ -12090,12 +12134,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -12120,7 +12164,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
@@ -12134,12 +12182,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -12156,7 +12204,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.1073/pnas.1700291115</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -12164,7 +12212,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
@@ -12173,22 +12225,22 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.1073/pnas.1700294115</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.1073/pnas.1700294115</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.1073/pnas.1700291115</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>duplicate_exact</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12252,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1073/pnas.1700291115</t>
+          <t>https://doi.org/10.1073/pnas.1700295114</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -12208,7 +12260,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
@@ -12222,17 +12278,17 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1700291115</t>
+          <t>https://doi.org/10.1073/pnas.1700291115</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1700294115</t>
+          <t>https://doi.org/10.1073/pnas.1700295114</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12300,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1073/pnas.1700295114</t>
+          <t>https://doi.org/10.1038/ngeo721</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -12252,7 +12308,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
@@ -12261,22 +12321,22 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1073/pnas.1700295114</t>
+          <t>https://doi.org/10.1038/ngeo2516</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1700295114</t>
+          <t>https://doi.org/10.1038/ngeo2516</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1700294115</t>
+          <t>https://doi.org/10.1038/ngeo721</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12348,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/ngeo721</t>
+          <t>https://doi.org/10.1038/ngeo2413</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12296,7 +12356,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
@@ -12305,17 +12369,17 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1038/ngeo2413</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/ngeo2413</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1038/ngeo721</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1038/ngeo721</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1038/ngeo2516</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -12362,12 +12426,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.6hdr7sqzx</t>
+          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.6hdr7sqzx</t>
+          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -12392,7 +12456,11 @@
           <t>URL DOI</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
@@ -12406,12 +12474,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -12458,12 +12526,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -12510,12 +12578,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -12562,12 +12630,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -12614,12 +12682,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -12666,12 +12734,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -12718,12 +12786,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -12770,12 +12838,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -12822,12 +12890,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -12869,22 +12937,22 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
           <t>https://doi.org/10.5281/zenodo.18392043</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392043</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
-        </is>
-      </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -12926,12 +12994,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -12978,12 +13046,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -13030,12 +13098,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -13082,12 +13150,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -13134,12 +13202,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>https://www.digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
+          <t>https://digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>https://www.digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
+          <t>https://digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -13186,12 +13254,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>https://www.digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
+          <t>https://digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>https://www.digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
+          <t>https://digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -13238,12 +13306,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>https://www.digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
+          <t>https://digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>https://www.digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
+          <t>https://digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -13270,7 +13338,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -13322,7 +13390,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -13342,12 +13410,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>https://www.github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
+          <t>https://github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>https://www.github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
+          <t>https://github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -13374,7 +13442,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -13394,12 +13462,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>https://www.github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
+          <t>https://github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>https://www.github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
+          <t>https://github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -13446,12 +13514,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
+          <t>https://doi.org/10.5281/zenodo.18392042</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -13498,12 +13566,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -13550,12 +13618,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arXiv.2412.15687</t>
+          <t>https://doi.org/10.48550/arXiv.2412.15687</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arXiv.2412.15687</t>
+          <t>https://doi.org/10.48550/arXiv.2412.15687</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -13602,12 +13670,12 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -13654,17 +13722,17 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392043</t>
+          <t>https://doi.org/10.5281/zenodo.18392043</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
+          <t>https://doi.org/10.5281/zenodo.18392043</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13774,12 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/qj.3293</t>
+          <t>https://doi.org/10.1002/qj.3293</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/qj.3293</t>
+          <t>https://doi.org/10.1002/qj.3293</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -13758,12 +13826,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/MWR-D-19-0323.1</t>
+          <t>https://doi.org/10.1175/MWR-D-19-0323.1</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/MWR-D-19-0323.1</t>
+          <t>https://doi.org/10.1175/MWR-D-19-0323.1</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -13810,12 +13878,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/MWR-D-19-0323.1</t>
+          <t>https://doi.org/10.1175/MWR-D-19-0323.1</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/MWR-D-19-0323.1</t>
+          <t>https://doi.org/10.1175/MWR-D-19-0323.1</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -13862,12 +13930,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/BAMS-D-23-0162.1</t>
+          <t>https://doi.org/10.1175/BAMS-D-23-0162.1</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/BAMS-D-23-0162.1</t>
+          <t>https://doi.org/10.1175/BAMS-D-23-0162.1</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -13914,12 +13982,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -13966,12 +14034,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -14070,12 +14138,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>https://www.data-nifc.opendata.arcgis.com/datasets/nifc::wfigs-interagency-fire-perimeters/about</t>
+          <t>https://data-nifc.opendata.arcgis.com/datasets/nifc::wfigs-interagency-fire-perimeters/about</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>https://www.data-nifc.opendata.arcgis.com/datasets/nifc::wfigs-interagency-fire-perimeters/about</t>
+          <t>https://data-nifc.opendata.arcgis.com/datasets/nifc::wfigs-interagency-fire-perimeters/about</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -14174,12 +14242,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>https://www.data-nifc.opendata.arcgis.com/datasets/nifc::interagencyfireperimeterhistory-all-years-view/about</t>
+          <t>https://data-nifc.opendata.arcgis.com/datasets/nifc::interagencyfireperimeterhistory-all-years-view/about</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>https://www.data-nifc.opendata.arcgis.com/datasets/nifc::interagencyfireperimeterhistory-all-years-view/about</t>
+          <t>https://data-nifc.opendata.arcgis.com/datasets/nifc::interagencyfireperimeterhistory-all-years-view/about</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -14226,12 +14294,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -14278,12 +14346,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -14330,12 +14398,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -14382,12 +14450,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -14434,12 +14502,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -14486,12 +14554,12 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -14538,12 +14606,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -14590,12 +14658,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.63xsj3vd4</t>
+          <t>https://doi.org/10.5061/dryad.63xsj3vd4</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.63xsj3vd4</t>
+          <t>https://doi.org/10.5061/dryad.63xsj3vd4</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -14642,12 +14710,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -14694,12 +14762,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025-supplement</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025-supplement</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -14746,12 +14814,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -14788,27 +14856,27 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>essd-17-7359-2025.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1016/j.rse.2019.02.015</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.rse.2019.02.015</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.rse.2016.02.054</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.rse.2016.02.054</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.rse.2019.02.015</t>
-        </is>
-      </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -14840,27 +14908,27 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>essd-17-7359-2025.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1016/j.rse.2012.12.003</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.rse.2012.12.003</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.rse.2013.12.008</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.rse.2013.12.008</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>https://www.doi.org/10.1016/j.rse.2012.12.003</t>
-        </is>
-      </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>duplicate_similar</t>
+          <t>duplicate_similar_replaced_by_simpler</t>
         </is>
       </c>
     </row>
@@ -14902,12 +14970,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.2737/RDS-2013-0009.6</t>
+          <t>https://doi.org/10.2737/RDS-2013-0009.6</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.2737/RDS-2013-0009.6</t>
+          <t>https://doi.org/10.2737/RDS-2013-0009.6</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -14954,12 +15022,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -15006,12 +15074,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.63xsj3vd4</t>
+          <t>https://doi.org/10.5061/dryad.63xsj3vd4</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.63xsj3vd4</t>
+          <t>https://doi.org/10.5061/dryad.63xsj3vd4</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -15058,12 +15126,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17298252</t>
+          <t>https://doi.org/10.5281/zenodo.17298252</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17298252</t>
+          <t>https://doi.org/10.5281/zenodo.17298252</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -15110,12 +15178,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
